--- a/outputs/daily/hr_rankings_2026-10-10.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-10.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,11 +784,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>66.8</v>
+        <v>70.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>54.7</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>53.2</v>
+        <v>56.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>54.7</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.3</v>
+        <v>55.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>54.7</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>51.9</v>
+        <v>55.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1648,10 @@
         <v>47</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -1649,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1824,8 +1832,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1864,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>49.9</v>
+        <v>53.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1928,10 @@
         <v>47</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -1925,39 +1941,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -2100,8 +2112,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2140,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2164,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>49.2</v>
+        <v>52.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,7 +2198,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2188,10 +2208,10 @@
         <v>54.7</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -2201,39 +2221,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2376,8 +2392,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2416,12 +2440,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2440,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.6</v>
+        <v>51.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2464,10 +2488,10 @@
         <v>54.7</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S8" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -2477,39 +2501,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2652,8 +2672,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2692,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2716,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>46.6</v>
+        <v>50.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2768,10 @@
         <v>47</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -2753,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2952,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2968,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45.2</v>
+        <v>48.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3048,10 @@
         <v>54.7</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -3029,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3204,8 +3232,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3224,7 +3260,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3244,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>44.7</v>
+        <v>48.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3292,10 +3328,10 @@
         <v>44.9</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
         <v>75</v>
@@ -3305,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3480,8 +3512,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3495,24 +3535,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -3520,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3530,12 +3570,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>42.3</v>
+        <v>46.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,65 +3598,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>53.5</v>
+        <v>44.9</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T12" t="n">
         <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>45</v>
+        <v>48.7</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3633,131 +3669,139 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>25.86</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>30.98</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3771,24 +3815,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>686668</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -3796,22 +3840,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>41.5</v>
+        <v>44.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,62 +3878,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>28.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.9</v>
+        <v>54.7</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>82</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3909,7 +3949,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -3919,121 +3959,129 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.34</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>99.9948</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1259</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2615</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1332</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>30.98</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>25.86</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4047,12 +4095,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4072,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>41.1</v>
+        <v>43.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,65 +4158,61 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>44.9</v>
+        <v>47</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>36.3</v>
+        <v>12</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4185,7 +4229,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -4195,17 +4239,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4215,67 +4259,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -4308,8 +4352,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4348,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.2</v>
+        <v>42.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,7 +4438,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4396,10 +4448,10 @@
         <v>54.7</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
@@ -4409,39 +4461,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4584,8 +4632,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4599,24 +4655,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -4624,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4634,12 +4690,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4648,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>38.5</v>
+        <v>42</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,65 +4718,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>20.9</v>
+        <v>13.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>47</v>
+        <v>54.7</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>12</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4737,131 +4789,139 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>30.98</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>25.86</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4900,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4924,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>38.1</v>
+        <v>41.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,7 +4998,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -4948,10 +5008,10 @@
         <v>47</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S17" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -4961,39 +5021,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5136,8 +5192,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5151,24 +5215,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -5176,22 +5240,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.7</v>
+        <v>39.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,62 +5278,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>54.7</v>
+        <v>44.9</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>77.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5294,7 +5354,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5309,111 +5369,119 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>25.86</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>30.98</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5427,12 +5495,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5452,12 +5520,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.5</v>
+        <v>37.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,62 +5558,58 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>13.7</v>
+        <v>7.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.9</v>
+        <v>47</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>72.7</v>
+        <v>38.3</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5565,27 +5629,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5595,67 +5659,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -5688,8 +5752,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6054,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6078,11 +6150,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>66.8</v>
+        <v>70.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>54.7</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6330,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>53.2</v>
+        <v>56.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>54.7</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6638,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6606,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.3</v>
+        <v>55.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6734,10 @@
         <v>54.7</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -6667,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6918,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6882,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>51.9</v>
+        <v>55.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7014,10 @@
         <v>47</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -6943,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7118,8 +7198,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7158,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>49.9</v>
+        <v>53.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7294,10 @@
         <v>47</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -7219,39 +7307,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7394,8 +7478,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7434,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7458,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>49.2</v>
+        <v>52.8</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,7 +7564,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7482,10 +7574,10 @@
         <v>54.7</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -7495,39 +7587,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7670,8 +7758,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7710,12 +7806,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7734,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.6</v>
+        <v>51.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7758,10 +7854,10 @@
         <v>54.7</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S8" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -7771,39 +7867,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7946,8 +8038,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7986,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8010,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>46.6</v>
+        <v>50.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8134,10 @@
         <v>47</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -8047,39 +8147,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8318,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8262,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45.2</v>
+        <v>48.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8414,10 @@
         <v>54.7</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -8323,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8498,8 +8598,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8518,7 +8626,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8538,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>44.7</v>
+        <v>48.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,7 +8684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8586,10 +8694,10 @@
         <v>44.9</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
         <v>75</v>
@@ -8599,39 +8707,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8774,8 +8878,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8789,24 +8901,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -8814,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8824,12 +8936,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>42.3</v>
+        <v>46.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,65 +8964,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>53.5</v>
+        <v>44.9</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T12" t="n">
         <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>45</v>
+        <v>48.7</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8927,131 +9035,139 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>25.86</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>30.98</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9065,24 +9181,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>686668</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -9090,22 +9206,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>41.5</v>
+        <v>44.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,62 +9244,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>28.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.9</v>
+        <v>54.7</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>82</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9203,7 +9315,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -9213,121 +9325,129 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.34</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>99.9948</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1259</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2615</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1332</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>30.98</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>25.86</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9341,12 +9461,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9366,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>41.1</v>
+        <v>43.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,65 +9524,61 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>44.9</v>
+        <v>47</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>36.3</v>
+        <v>12</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -9479,7 +9595,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -9489,17 +9605,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9509,67 +9625,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -9602,8 +9718,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9642,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39.2</v>
+        <v>42.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,7 +9804,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9690,10 +9814,10 @@
         <v>54.7</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
@@ -9703,39 +9827,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9878,8 +9998,16 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9893,24 +10021,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -9918,7 +10046,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -9928,12 +10056,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9942,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>38.5</v>
+        <v>42</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,65 +10084,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>20.9</v>
+        <v>13.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>47</v>
+        <v>54.7</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>12</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10031,131 +10155,139 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>30.98</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>25.86</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10194,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10218,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>38.1</v>
+        <v>41.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,7 +10364,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10242,10 +10374,10 @@
         <v>47</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S17" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -10255,39 +10387,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10430,8 +10558,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10445,24 +10581,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -10470,22 +10606,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36.7</v>
+        <v>39.1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,62 +10644,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>54.7</v>
+        <v>44.9</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>77.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10588,7 +10720,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10603,111 +10735,119 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>25.86</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>30.98</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10721,12 +10861,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10746,12 +10886,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>35.5</v>
+        <v>37.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,62 +10924,58 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>13.7</v>
+        <v>7.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.9</v>
+        <v>47</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>47.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>72.7</v>
+        <v>38.3</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10859,27 +10995,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -10889,67 +11025,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10982,8 +11118,16 @@
           <t>30.98</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>

--- a/outputs/daily/hr_rankings_2026-10-10.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-10.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>70.5</v>
+        <v>73</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>54.7</v>
       </c>
       <c r="R2" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>56.9</v>
+        <v>59.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>54.7</v>
       </c>
       <c r="R3" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>55.9</v>
+        <v>58.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>54.7</v>
       </c>
       <c r="R4" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.6</v>
+        <v>58.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>47</v>
       </c>
       <c r="R5" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>94.90000000000001</v>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.5</v>
+        <v>56.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>47</v>
       </c>
       <c r="R6" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.8</v>
+        <v>55.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>54.7</v>
       </c>
       <c r="R7" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>86.40000000000001</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51.3</v>
+        <v>53.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>54.7</v>
       </c>
       <c r="R8" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>52.4</v>
@@ -2674,12 +2674,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>50.2</v>
+        <v>52.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>47</v>
       </c>
       <c r="R9" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>86.40000000000001</v>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>48.9</v>
+        <v>51.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>54.7</v>
       </c>
       <c r="R10" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>48.3</v>
+        <v>50.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44.9</v>
       </c>
       <c r="R11" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -3514,12 +3514,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>46.8</v>
+        <v>49.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>44.9</v>
       </c>
       <c r="R12" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>64.3</v>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>44.6</v>
+        <v>47.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>54.7</v>
       </c>
       <c r="R13" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>44.8</v>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.8</v>
+        <v>46.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>47</v>
       </c>
       <c r="R14" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42.9</v>
+        <v>45.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>54.7</v>
       </c>
       <c r="R15" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>44.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>54.7</v>
       </c>
       <c r="R16" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.8</v>
+        <v>44.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>47</v>
       </c>
       <c r="R17" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>93.2</v>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>39.1</v>
+        <v>41.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>44.9</v>
       </c>
       <c r="R18" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>37.2</v>
+        <v>39.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>47</v>
       </c>
       <c r="R19" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>70.5</v>
+        <v>73</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>54.7</v>
       </c>
       <c r="R2" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>56.9</v>
+        <v>59.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>54.7</v>
       </c>
       <c r="R3" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>55.9</v>
+        <v>58.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>54.7</v>
       </c>
       <c r="R4" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -6920,12 +6920,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.6</v>
+        <v>58.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>47</v>
       </c>
       <c r="R5" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>94.90000000000001</v>
@@ -7200,12 +7200,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>53.5</v>
+        <v>56.1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>47</v>
       </c>
       <c r="R6" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.8</v>
+        <v>55.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>54.7</v>
       </c>
       <c r="R7" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
         <v>86.40000000000001</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51.3</v>
+        <v>53.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>54.7</v>
       </c>
       <c r="R8" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>52.4</v>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>50.2</v>
+        <v>52.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>47</v>
       </c>
       <c r="R9" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>86.40000000000001</v>
@@ -8320,12 +8320,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>48.9</v>
+        <v>51.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>54.7</v>
       </c>
       <c r="R10" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -8600,12 +8600,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>48.3</v>
+        <v>50.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>44.9</v>
       </c>
       <c r="R11" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>46.8</v>
+        <v>49.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44.9</v>
       </c>
       <c r="R12" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>64.3</v>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>44.6</v>
+        <v>47.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>54.7</v>
       </c>
       <c r="R13" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>44.8</v>
@@ -9440,12 +9440,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.8</v>
+        <v>46.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>47</v>
       </c>
       <c r="R14" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42.9</v>
+        <v>45.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>54.7</v>
       </c>
       <c r="R15" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -10000,12 +10000,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10070,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>44.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>54.7</v>
       </c>
       <c r="R16" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10350,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.8</v>
+        <v>44.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>47</v>
       </c>
       <c r="R17" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S17" t="n">
         <v>93.2</v>
@@ -10560,12 +10560,12 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>39.1</v>
+        <v>41.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>44.9</v>
       </c>
       <c r="R18" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -10840,12 +10840,12 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>37.2</v>
+        <v>39.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>47</v>
       </c>
       <c r="R19" t="n">
-        <v>47.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -11120,12 +11120,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
